--- a/data/trans_orig/IP3102-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3102-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14162</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>9983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>22236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15447</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>33461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33860</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49147</t>
+          <t>49463</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30009</t>
+          <t>29679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44969</t>
+          <t>44592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67602</t>
+          <t>67942</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89933</t>
+          <t>89052</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>28362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>24173</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38443</t>
+          <t>38516</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>42570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62122</t>
+          <t>62827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20026</t>
+          <t>19591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>15100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28643</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8827</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13586</t>
+          <t>13170</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>23547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22265</t>
+          <t>22549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38860</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25038</t>
+          <t>24893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>39027</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>38000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>52382</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72311</t>
+          <t>72360</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29259</t>
+          <t>28997</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21383</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28541</t>
+          <t>29188</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45990</t>
+          <t>45698</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22405</t>
+          <t>22943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17606</t>
+          <t>17571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32282</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7948</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17233</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30950</t>
+          <t>30326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25290</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42098</t>
+          <t>42129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>29299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26322</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41314</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47526</t>
+          <t>47998</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66333</t>
+          <t>67317</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24189</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14098</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27067</t>
+          <t>26302</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28724</t>
+          <t>28760</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46076</t>
+          <t>45603</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>14871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>16864</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30633</t>
+          <t>30652</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>8979</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15851</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>30836</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40038</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27427</t>
+          <t>26892</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44380</t>
+          <t>44299</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55269</t>
+          <t>54845</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79324</t>
+          <t>78946</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61391</t>
+          <t>58292</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81689</t>
+          <t>81368</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64836</t>
+          <t>64883</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87056</t>
+          <t>86392</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>131533</t>
+          <t>129472</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>162096</t>
+          <t>161517</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,04%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37102</t>
+          <t>37222</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55092</t>
+          <t>56329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31181</t>
+          <t>31477</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48349</t>
+          <t>49627</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73612</t>
+          <t>73860</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>99918</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25169</t>
+          <t>25285</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42418</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15860</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>28836</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43920</t>
+          <t>44295</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>64877</t>
+          <t>66139</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14561</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21581</t>
+          <t>20381</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31823</t>
+          <t>31264</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22208</t>
+          <t>21718</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20525</t>
+          <t>21457</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34007</t>
+          <t>34407</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52449</t>
+          <t>53118</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34161</t>
+          <t>33708</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50159</t>
+          <t>49845</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32471</t>
+          <t>32742</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>48276</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>69838</t>
+          <t>71584</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>92616</t>
+          <t>92968</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14540</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>27257</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>38012</t>
+          <t>37606</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>57664</t>
+          <t>56633</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18824</t>
+          <t>18021</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15653</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>15539</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>29711</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14142</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26584</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>27675</t>
+          <t>27623</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>32227</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>49402</t>
+          <t>49672</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>20703</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>34214</t>
+          <t>34481</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>19858</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>32443</t>
+          <t>31827</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>44399</t>
+          <t>44100</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>63087</t>
+          <t>62726</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>20513</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7376</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>19231</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>34458</t>
+          <t>34494</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>15529</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>26373</t>
+          <t>27564</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>45770</t>
+          <t>45916</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>32216</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>52545</t>
+          <t>52700</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>64537</t>
+          <t>65424</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>92515</t>
+          <t>92278</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>89674</t>
+          <t>89756</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>119986</t>
+          <t>120485</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>118628</t>
+          <t>119494</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>151809</t>
+          <t>151936</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>216337</t>
+          <t>217822</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>262535</t>
+          <t>261377</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>214151</t>
+          <t>216175</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>254750</t>
+          <t>254132</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>222819</t>
+          <t>225965</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>263076</t>
+          <t>264534</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>455048</t>
+          <t>453458</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>506395</t>
+          <t>505000</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>124596</t>
+          <t>126453</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>159713</t>
+          <t>158026</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>127673</t>
+          <t>125373</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>159259</t>
+          <t>158853</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>260362</t>
+          <t>258894</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>307699</t>
+          <t>307394</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>68172</t>
+          <t>67164</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>94313</t>
+          <t>93560</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>62632</t>
+          <t>62597</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>88022</t>
+          <t>87874</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>136302</t>
+          <t>136560</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>174384</t>
+          <t>173853</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16499</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19277</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34766</t>
+          <t>33893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>22222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22687</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37156</t>
+          <t>37876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37668</t>
+          <t>37387</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56403</t>
+          <t>55662</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>17302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>20278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>18820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34370</t>
+          <t>33736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34594</t>
+          <t>33072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49712</t>
+          <t>48350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17247</t>
+          <t>15993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30455</t>
+          <t>29960</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54873</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74884</t>
+          <t>75165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>429</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>19026</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>21086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36989</t>
+          <t>36691</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18859</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32602</t>
+          <t>32561</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>18033</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>32025</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40849</t>
+          <t>40814</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60822</t>
+          <t>60596</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>8977</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>20235</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19560</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>34892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35500</t>
+          <t>36375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29776</t>
+          <t>29673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45390</t>
+          <t>45360</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56166</t>
+          <t>55718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>76882</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>8878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>25376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42493</t>
+          <t>42641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22834</t>
+          <t>22653</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37197</t>
+          <t>36783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33009</t>
+          <t>32837</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46109</t>
+          <t>45589</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65904</t>
+          <t>65219</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16348</t>
+          <t>16737</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17262</t>
+          <t>17331</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32376</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>12022</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>24477</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18826</t>
+          <t>19296</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32480</t>
+          <t>32755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34413</t>
+          <t>34105</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>52054</t>
+          <t>52392</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14003</t>
+          <t>13715</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>20519</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23424</t>
+          <t>22973</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40429</t>
+          <t>39590</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>43256</t>
+          <t>43533</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63909</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>71292</t>
+          <t>71586</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>98044</t>
+          <t>97614</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61520</t>
+          <t>61726</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83079</t>
+          <t>83674</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51973</t>
+          <t>52002</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73358</t>
+          <t>73380</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>119429</t>
+          <t>119443</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>151457</t>
+          <t>149730</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27521</t>
+          <t>27237</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45344</t>
+          <t>45390</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44295</t>
+          <t>44284</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58845</t>
+          <t>56052</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83396</t>
+          <t>81857</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31503</t>
+          <t>31624</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
+          <t>50305</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38058</t>
+          <t>37588</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58461</t>
+          <t>58541</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>74556</t>
+          <t>75388</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>101716</t>
+          <t>101513</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21492</t>
+          <t>21426</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21255</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37305</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21860</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37043</t>
+          <t>36838</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46799</t>
+          <t>45618</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69199</t>
+          <t>68803</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>28202</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45629</t>
+          <t>45435</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>23240</t>
+          <t>22809</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>39445</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>55721</t>
+          <t>55731</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79050</t>
+          <t>79339</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21473</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36939</t>
+          <t>35575</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>19523</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>33886</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>43809</t>
+          <t>43963</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>65637</t>
+          <t>64904</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31183</t>
+          <t>31119</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>47995</t>
+          <t>48476</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26934</t>
+          <t>26691</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>44848</t>
+          <t>43691</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>62241</t>
+          <t>63744</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>87173</t>
+          <t>88064</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10482</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>22320</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13509</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>24741</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>24507</t>
+          <t>24491</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>37632</t>
+          <t>37649</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>41345</t>
+          <t>41599</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>59286</t>
+          <t>59046</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,9%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9658</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>22497</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13328</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>27473</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>27997</t>
+          <t>28569</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33641</t>
+          <t>32883</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>36044</t>
+          <t>34740</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>57553</t>
+          <t>56907</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>99064</t>
+          <t>100451</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>131084</t>
+          <t>132066</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>120461</t>
+          <t>119934</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>153512</t>
+          <t>152839</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>226826</t>
+          <t>229604</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>274360</t>
+          <t>274989</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>180380</t>
+          <t>179524</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>218734</t>
+          <t>218723</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>184893</t>
+          <t>186285</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>224553</t>
+          <t>223838</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>374688</t>
+          <t>377774</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>429929</t>
+          <t>432660</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>93499</t>
+          <t>93712</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>123382</t>
+          <t>123370</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>94096</t>
+          <t>94063</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>126703</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>192971</t>
+          <t>193428</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>237426</t>
+          <t>236908</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>160911</t>
+          <t>161424</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>198922</t>
+          <t>197357</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>156917</t>
+          <t>159043</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>195275</t>
+          <t>196153</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>329681</t>
+          <t>329194</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>385141</t>
+          <t>384319</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17472</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17700</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32543</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26913</t>
+          <t>27149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26714</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43510</t>
+          <t>44751</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>14142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26292</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31190</t>
+          <t>32579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49313</t>
+          <t>50491</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18018</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30814</t>
+          <t>31340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28375</t>
+          <t>28760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42579</t>
+          <t>43837</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48650</t>
+          <t>49528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>70787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23907</t>
+          <t>24367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16218</t>
+          <t>15833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>20503</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36543</t>
+          <t>36038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35016</t>
+          <t>33778</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25469</t>
+          <t>25299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40482</t>
+          <t>41294</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49016</t>
+          <t>49434</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70003</t>
+          <t>69978</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27428</t>
+          <t>26585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>20634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35629</t>
+          <t>36530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37364</t>
+          <t>37181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57864</t>
+          <t>57006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22695</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38028</t>
+          <t>37113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>20414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>34995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46570</t>
+          <t>47261</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67191</t>
+          <t>67577</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1538</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8947</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19454</t>
+          <t>19726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35262</t>
+          <t>35181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21931</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23973</t>
+          <t>23622</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25530</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>40833</t>
+          <t>42522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23344</t>
+          <t>23432</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25066</t>
+          <t>24298</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40879</t>
+          <t>39973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26843</t>
+          <t>26404</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>23430</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38909</t>
+          <t>39218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4541</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8844</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20933</t>
+          <t>20696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>15520</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30223</t>
+          <t>29710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>26939</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44126</t>
+          <t>44296</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23425</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40754</t>
+          <t>40375</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53749</t>
+          <t>54669</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78256</t>
+          <t>79405</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41414</t>
+          <t>41733</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>61028</t>
+          <t>61046</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53376</t>
+          <t>52847</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>80138</t>
+          <t>78619</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>107719</t>
+          <t>105815</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39328</t>
+          <t>39663</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59459</t>
+          <t>58921</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>39422</t>
+          <t>40072</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59652</t>
+          <t>60135</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>85600</t>
+          <t>83907</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>113283</t>
+          <t>112223</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54781</t>
+          <t>54713</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75529</t>
+          <t>75495</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52691</t>
+          <t>53127</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>74208</t>
+          <t>74572</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>114166</t>
+          <t>115417</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>144990</t>
+          <t>144980</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12490</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5974</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15782</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>25452</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>14507</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28135</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>20717</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>26581</t>
+          <t>25730</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>44669</t>
+          <t>44005</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20035</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34908</t>
+          <t>35535</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22703</t>
+          <t>22149</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>38100</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>45417</t>
+          <t>46056</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>68653</t>
+          <t>68166</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19552</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34780</t>
+          <t>34940</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37076</t>
+          <t>37320</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>68432</t>
+          <t>66917</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>41002</t>
+          <t>42114</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>59749</t>
+          <t>60510</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>43631</t>
+          <t>43191</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>61105</t>
+          <t>61623</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>89883</t>
+          <t>89330</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>115523</t>
+          <t>115345</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>878</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18359</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29708</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>13232</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25416</t>
+          <t>25056</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>26247</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>31066</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>48921</t>
+          <t>47582</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>15862</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>27393</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>22541</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>25866</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>27630</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>43972</t>
+          <t>44033</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>18224</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35023</t>
+          <t>34266</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>28421</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>48175</t>
+          <t>49098</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>51029</t>
+          <t>51266</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>76844</t>
+          <t>76710</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>92907</t>
+          <t>92551</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>123086</t>
+          <t>124180</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>79010</t>
+          <t>79330</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>109301</t>
+          <t>109475</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>177259</t>
+          <t>179677</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>221669</t>
+          <t>222579</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>135923</t>
+          <t>135876</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>170949</t>
+          <t>172181</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>145975</t>
+          <t>145615</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>182661</t>
+          <t>181845</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>289445</t>
+          <t>288556</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>340554</t>
+          <t>340026</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>122639</t>
+          <t>125498</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>158205</t>
+          <t>156934</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>133712</t>
+          <t>134661</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>171995</t>
+          <t>170992</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>268620</t>
+          <t>268538</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>317527</t>
+          <t>320317</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>175779</t>
+          <t>178493</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>215136</t>
+          <t>215187</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>197368</t>
+          <t>198250</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>238183</t>
+          <t>237430</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>384682</t>
+          <t>387504</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>439616</t>
+          <t>440886</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
